--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260717.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.98%</t>
+          <t>27.60%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.80%</t>
+          <t>8.95%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.72%</t>
+          <t>6.82%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>5.84%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -792,29 +792,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,125</t>
+          <t>194,537,408</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -836,161 +836,161 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,320</t>
+          <t>22,125</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>57,185</t>
+          <t>35,320</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,695</t>
+          <t>57,185</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>86,215</t>
+          <t>22,695</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>112,926,908</t>
+          <t>86,215</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,728</t>
+          <t>21,820</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>21,820</t>
+          <t>29,728</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1034,46 +1034,46 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,890</t>
+          <t>23,938</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,938</t>
+          <t>8,890</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,154 +1085,154 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,666,721</t>
+          <t>142,055</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>142,055</t>
+          <t>20,635</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,635</t>
+          <t>13,051</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>13,051</t>
+          <t>10,766</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10,766</t>
+          <t>17,781</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,781</t>
+          <t>42,130</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,130</t>
+          <t>48,400</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1254,73 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>48,400</t>
+          <t>21,937</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>21,937</t>
+          <t>1,166,721</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>48,280,500</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
